--- a/data/base_vendas_24.xlsx
+++ b/data/base_vendas_24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EdvaldoGuilhermePaiv\Documents\GitHub\projeto-vendas-streamlit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44120216-93FC-4D03-B127-0678BC7985B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8388542-28A2-4C9A-A5A1-FCCABC9BE37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E02EEFDF-8306-4398-969E-76D18EC37986}"/>
   </bookViews>
